--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N63_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N63_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>64.63120590370043</v>
+        <v>10.50257095935132</v>
       </c>
       <c r="D2" t="n">
-        <v>65.14404763056923</v>
+        <v>10.5859077399675</v>
       </c>
       <c r="E2" t="n">
-        <v>14.20329729361948</v>
+        <v>2.308035810213166</v>
       </c>
       <c r="F2" t="n">
-        <v>14.48905039156655</v>
+        <v>2.354470688629564</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.1166905536857</v>
+        <v>6.193962214973927</v>
       </c>
       <c r="D3" t="n">
-        <v>38.80570003949878</v>
+        <v>6.305926256418553</v>
       </c>
       <c r="E3" t="n">
-        <v>14.20329729361948</v>
+        <v>2.308035810213166</v>
       </c>
       <c r="F3" t="n">
-        <v>14.48905039156655</v>
+        <v>2.354470688629564</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.86659577212946</v>
+        <v>5.178321812971038</v>
       </c>
       <c r="D4" t="n">
-        <v>31.3735340666825</v>
+        <v>5.098199285835907</v>
       </c>
       <c r="E4" t="n">
-        <v>14.20329729361948</v>
+        <v>2.308035810213166</v>
       </c>
       <c r="F4" t="n">
-        <v>14.48905039156655</v>
+        <v>2.354470688629564</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
